--- a/content/member-assets/gym-churn-report/churn-report-template.xlsx
+++ b/content/member-assets/gym-churn-report/churn-report-template.xlsx
@@ -17,10 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -77,7 +78,7 @@
       </bottom>
     </border>
   </borders>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -96,7 +97,49 @@
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF8F0"/>
+        </patternFill>
+      </fill>
+      <font>
+        <color rgb="FF0F6B3F"/>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF4E8"/>
+        </patternFill>
+      </fill>
+      <font>
+        <color rgb="FF8A4B00"/>
+        <b/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -107,10 +150,8 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -119,19 +160,14 @@
           <t>Side Hustle Stephen - The Launchpad</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr" s="6">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="6">
         <is>
           <t>Churn Report Template</t>
         </is>
@@ -150,12 +186,12 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr" s="6">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t>A spreadsheet for tagging cancellations and surfacing trends.</t>
         </is>
@@ -174,12 +210,12 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" t="inlineStr" s="2">
+      <c r="A6" t="inlineStr" s="6">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="6">
         <is>
           <t>B2B Service</t>
         </is>
@@ -198,12 +234,12 @@
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" t="inlineStr" s="2">
+      <c r="A8" t="inlineStr" s="6">
         <is>
           <t>Time to first sale</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="2">
+      <c r="B8" t="inlineStr" s="6">
         <is>
           <t>2-4 weeks</t>
         </is>
@@ -222,12 +258,12 @@
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" t="inlineStr" s="2">
+      <c r="A10" t="inlineStr" s="6">
         <is>
           <t>How to use</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="2">
+      <c r="B10" t="inlineStr" s="6">
         <is>
           <t>Work left to right through the tabs. Replace the sample values, keep the formulas, and verify every fact before client use.</t>
         </is>
@@ -246,9 +282,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Start Here&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -259,10 +298,8 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -278,10 +315,10 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="6">
         <is>
           <t>Paste every cancellation into Raw Cancellations.</t>
         </is>
@@ -298,10 +335,10 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="4">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t>Review Dashboard before the monthly retention call.</t>
         </is>
@@ -318,9 +355,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Instructions&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -331,10 +371,12 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -370,40 +412,36 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="A2" s="11">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="inlineStr" s="6">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr" s="6">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="7">
         <v>189</v>
       </c>
-      <c r="E2" t="inlineStr" s="2">
+      <c r="E2" t="inlineStr" s="6">
         <is>
           <t>Pause plan</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr" s="2">
+      <c r="F2" t="inlineStr" s="6">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" t="inlineStr" s="2">
-        <is>
-          <t>2026-06-03</t>
-        </is>
+      <c r="A3" s="10">
+        <v>46176</v>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
@@ -430,40 +468,36 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="A4" s="11">
+        <v>46178</v>
+      </c>
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="6">
         <is>
           <t>Experience</t>
         </is>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="7">
         <v>189</v>
       </c>
-      <c r="E4" t="inlineStr" s="2">
+      <c r="E4" t="inlineStr" s="6">
         <is>
           <t>Owner call</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr" s="2">
+      <c r="F4" t="inlineStr" s="6">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" t="inlineStr" s="2">
-        <is>
-          <t>2026-06-07</t>
-        </is>
+      <c r="A5" s="10">
+        <v>46180</v>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
@@ -490,40 +524,36 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" t="inlineStr" s="2">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="A6" s="11">
+        <v>46183</v>
+      </c>
+      <c r="B6" t="inlineStr" s="6">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="6">
         <is>
           <t>Injury</t>
         </is>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="7">
         <v>189</v>
       </c>
-      <c r="E6" t="inlineStr" s="2">
+      <c r="E6" t="inlineStr" s="6">
         <is>
           <t>Freeze</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr" s="2">
+      <c r="F6" t="inlineStr" s="6">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" t="inlineStr" s="2">
-        <is>
-          <t>2026-06-12</t>
-        </is>
+      <c r="A7" s="10">
+        <v>46185</v>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
@@ -551,6 +581,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F7"/>
+  <conditionalFormatting sqref="F2:F200">
+    <cfRule type="containsText" operator="containsText" text="Done" dxfId="0" priority="16">
+      <formula>NOT(ISERROR(SEARCH("Done",F2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" operator="containsText" text="Approved" dxfId="0" priority="17">
+      <formula>NOT(ISERROR(SEARCH("Approved",F2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" operator="containsText" text="Open" dxfId="1" priority="18">
+      <formula>NOT(ISERROR(SEARCH("Open",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F2:F200">
       <formula1>"Open,In progress,Done,Yes,No,Approved"</formula1>
@@ -558,6 +599,10 @@
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Raw Cancellations&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -568,10 +613,9 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -592,15 +636,15 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr" s="6">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="7">
         <f>COUNTIF('Raw Cancellations'!C:C,A2)</f>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="7">
         <f>SUMIF('Raw Cancellations'!C:C,A2,'Raw Cancellations'!D:D)</f>
       </c>
     </row>
@@ -618,15 +662,15 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr" s="6">
         <is>
           <t>Experience</t>
         </is>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="8">
         <f>COUNTIF('Raw Cancellations'!C:C,A4)</f>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="7">
         <f>SUMIF('Raw Cancellations'!C:C,A4,'Raw Cancellations'!D:D)</f>
       </c>
     </row>
@@ -644,15 +688,15 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" t="inlineStr" s="2">
+      <c r="A6" t="inlineStr" s="6">
         <is>
           <t>Injury</t>
         </is>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="8">
         <f>COUNTIF('Raw Cancellations'!C:C,A6)</f>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="7">
         <f>SUMIF('Raw Cancellations'!C:C,A6,'Raw Cancellations'!D:D)</f>
       </c>
     </row>
@@ -660,6 +704,10 @@
   <autoFilter ref="A1:C6"/>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Tag Summary&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -670,10 +718,12 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -709,30 +759,28 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="6">
         <is>
           <t>Top churn tag</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr" s="6">
         <is>
           <t>Create save script for highest-risk reason</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="6">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr" s="2">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr" s="2">
+      <c r="E2" s="11">
+        <v>46208</v>
+      </c>
+      <c r="F2" t="inlineStr" s="6">
         <is>
           <t>Open</t>
         </is>
@@ -757,10 +805,8 @@
           <t>Manager</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr" s="2">
-        <is>
-          <t>2026-07-12</t>
-        </is>
+      <c r="E3" s="10">
+        <v>46215</v>
       </c>
       <c r="F3" t="inlineStr" s="2">
         <is>
@@ -769,37 +815,45 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="4">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t>Class timing</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="6">
         <is>
           <t>Compare cancelled members against attendance windows</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="2">
+      <c r="D4" t="inlineStr" s="6">
         <is>
           <t>Coach</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="2">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="2">
+      <c r="E4" s="11">
+        <v>46222</v>
+      </c>
+      <c r="F4" t="inlineStr" s="6">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <conditionalFormatting sqref="F2:F200">
+    <cfRule type="containsText" operator="containsText" text="Done" dxfId="0" priority="16">
+      <formula>NOT(ISERROR(SEARCH("Done",F2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" operator="containsText" text="Approved" dxfId="0" priority="17">
+      <formula>NOT(ISERROR(SEARCH("Approved",F2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" operator="containsText" text="Open" dxfId="1" priority="18">
+      <formula>NOT(ISERROR(SEARCH("Open",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F2:F200">
       <formula1>"Open,In progress,Done,Yes,No,Approved"</formula1>
@@ -807,6 +861,10 @@
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Action Plan&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -817,10 +875,8 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -836,12 +892,12 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr" s="6">
         <is>
           <t>Total cancellations</t>
         </is>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="8">
         <f>COUNTA('Raw Cancellations'!A2:A100)</f>
       </c>
     </row>
@@ -856,12 +912,12 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr" s="6">
         <is>
           <t>Save rate</t>
         </is>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="9">
         <f>IF(B2=0,"",B3/B2)</f>
       </c>
     </row>
@@ -876,12 +932,12 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" t="inlineStr" s="2">
+      <c r="A6" t="inlineStr" s="6">
         <is>
           <t>Top controllable reason</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="6">
         <is>
           <t>Review Tag Summary</t>
         </is>
@@ -900,9 +956,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Dashboard&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -913,10 +972,9 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -937,17 +995,17 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr" s="6">
         <is>
           <t>Top churn reason</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="6">
         <is>
           <t/>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr" s="6">
         <is>
           <t/>
         </is>
@@ -971,17 +1029,17 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr" s="6">
         <is>
           <t>Action owner</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t/>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="6">
         <is>
           <t/>
         </is>
@@ -1008,6 +1066,10 @@
   <autoFilter ref="A1:C5"/>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Call Notes&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1019,9 +1081,8 @@
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1042,17 +1103,17 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr" s="6">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="6">
         <is>
           <t>Churn Report Template</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr" s="6">
         <is>
           <t>Use this as the named deliverable in the proposal and handoff.</t>
         </is>
@@ -1076,17 +1137,17 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr" s="6">
         <is>
           <t>Priority decision</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t>Separate life-event churn from controllable churn before assigning actions.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="6">
         <is>
           <t>Use this to keep the delivery focused.</t>
         </is>
@@ -1110,17 +1171,17 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" t="inlineStr" s="2">
+      <c r="A6" t="inlineStr" s="6">
         <is>
           <t>Upsell path</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="6">
         <is>
           <t>The monthly call should end with three owner-assigned actions max.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="6">
         <is>
           <t>Use after the first asset is approved.</t>
         </is>
@@ -1130,6 +1191,10 @@
   <autoFilter ref="A1:C6"/>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Worked Example&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1140,10 +1205,10 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="8" width="24" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1169,22 +1234,22 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr" s="6">
         <is>
           <t>1. Collect</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="6">
         <is>
           <t>Gather source material and visible proof before editing.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr" s="6">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="6">
         <is>
           <t>Open</t>
         </is>
@@ -1213,22 +1278,22 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr" s="6">
         <is>
           <t>3. Flag</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t>Mark every uncertain fact, price, or claim for client approval.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="6">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="2">
+      <c r="D4" t="inlineStr" s="6">
         <is>
           <t>Open</t>
         </is>
@@ -1257,22 +1322,22 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" t="inlineStr" s="2">
+      <c r="A6" t="inlineStr" s="6">
         <is>
           <t>5. Deliver</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="6">
         <is>
           <t>Send working file, final export, and a summary of what changed.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="6">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="2">
+      <c r="D6" t="inlineStr" s="6">
         <is>
           <t>Open</t>
         </is>
@@ -1301,22 +1366,22 @@
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" t="inlineStr" s="2">
+      <c r="A8" t="inlineStr" s="6">
         <is>
           <t>QA - placeholders removed or marked</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="2">
+      <c r="B8" t="inlineStr" s="6">
         <is>
           <t>Required before sending</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="2">
+      <c r="C8" t="inlineStr" s="6">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="2">
+      <c r="D8" t="inlineStr" s="6">
         <is>
           <t>Open</t>
         </is>
@@ -1345,22 +1410,22 @@
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" t="inlineStr" s="2">
+      <c r="A10" t="inlineStr" s="6">
         <is>
           <t>QA - no guaranteed revenue/ranking/performance claims</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="2">
+      <c r="B10" t="inlineStr" s="6">
         <is>
           <t>Required before sending</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="2">
+      <c r="C10" t="inlineStr" s="6">
         <is>
           <t>You</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="2">
+      <c r="D10" t="inlineStr" s="6">
         <is>
           <t>Open</t>
         </is>
@@ -1390,6 +1455,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D11"/>
+  <conditionalFormatting sqref="D2:D200">
+    <cfRule type="containsText" operator="containsText" text="Done" dxfId="0" priority="10">
+      <formula>NOT(ISERROR(SEARCH("Done",D2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" operator="containsText" text="Approved" dxfId="0" priority="11">
+      <formula>NOT(ISERROR(SEARCH("Approved",D2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" operator="containsText" text="Open" dxfId="1" priority="12">
+      <formula>NOT(ISERROR(SEARCH("Open",D2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="D2:D200">
       <formula1>"Open,In progress,Done,Yes,No,Approved"</formula1>
@@ -1397,5 +1473,9 @@
   </dataValidations>
   <pageMargins left="0.45" right="0.45" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;LSide Hustle Stephen - Delivery &amp; QA&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LVerify facts before client use&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>